--- a/김남주바이오_각 품목별 코드 및 인코딩 데이터 정리.xlsx
+++ b/김남주바이오_각 품목별 코드 및 인코딩 데이터 정리.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. 삼화당 업무자료\## 프로그램 개발(엑세스+AI) 입출고 관리 시스템\통합버전(HP 입출고+UPS + 시설관리)\통합버전\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9675C3-1106-42DE-8251-4E7A50B08FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1A9675C3-1106-42DE-8251-4E7A50B08FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3142D395-5590-4DE8-851E-AB01E58801CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="304">
   <si>
     <t>제품코드</t>
   </si>
@@ -2439,6 +2439,14 @@
   </si>
   <si>
     <t>리니어발주(재발주)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDDD</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3227,7 +3235,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3730,16 +3738,40 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3749,9 +3781,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3777,33 +3806,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6306,82 +6308,82 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="182" t="s">
         <v>296</v>
       </c>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
       <c r="E2" s="44"/>
       <c r="F2" s="3"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="178" t="s">
+      <c r="B3" s="185" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="180" t="s">
+      <c r="C3" s="187" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="180" t="s">
+      <c r="D3" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="182" t="s">
+      <c r="E3" s="189" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="180" t="s">
+      <c r="F3" s="187" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="168" t="s">
+      <c r="H3" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="175"/>
+      <c r="I3" s="172"/>
       <c r="J3" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="172" t="s">
+      <c r="K3" s="180" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="168" t="s">
+      <c r="L3" s="178" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="169"/>
-      <c r="O3" s="169"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="169"/>
-      <c r="S3" s="169"/>
-      <c r="T3" s="169"/>
-      <c r="U3" s="187" t="s">
+      <c r="M3" s="179"/>
+      <c r="N3" s="179"/>
+      <c r="O3" s="179"/>
+      <c r="P3" s="179"/>
+      <c r="Q3" s="179"/>
+      <c r="R3" s="179"/>
+      <c r="S3" s="179"/>
+      <c r="T3" s="179"/>
+      <c r="U3" s="176" t="s">
         <v>72</v>
       </c>
       <c r="V3" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="175" t="s">
+      <c r="W3" s="172" t="s">
         <v>17</v>
       </c>
       <c r="X3" s="170" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="185" t="s">
+      <c r="Y3" s="174" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="177"/>
-      <c r="B4" s="179"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="181"/>
+      <c r="A4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="188"/>
       <c r="G4" s="171"/>
       <c r="H4" s="28" t="s">
         <v>38</v>
@@ -6390,7 +6392,7 @@
         <v>43</v>
       </c>
       <c r="J4" s="171"/>
-      <c r="K4" s="173"/>
+      <c r="K4" s="181"/>
       <c r="L4" s="134" t="s">
         <v>45</v>
       </c>
@@ -6418,11 +6420,11 @@
       <c r="T4" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="188"/>
+      <c r="U4" s="177"/>
       <c r="V4" s="171"/>
-      <c r="W4" s="184"/>
+      <c r="W4" s="173"/>
       <c r="X4" s="171"/>
-      <c r="Y4" s="186"/>
+      <c r="Y4" s="175"/>
     </row>
     <row r="5" spans="1:25" ht="50.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
@@ -8527,7 +8529,7 @@
       </c>
     </row>
     <row r="43" spans="1:25" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="189">
+      <c r="A43" s="78">
         <v>36</v>
       </c>
       <c r="B43" s="132">
@@ -8539,7 +8541,7 @@
       <c r="D43" s="74">
         <v>2</v>
       </c>
-      <c r="E43" s="190" t="s">
+      <c r="E43" s="168" t="s">
         <v>124</v>
       </c>
       <c r="F43" s="78"/>
@@ -8553,14 +8555,24 @@
       <c r="J43" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="K43" s="191" t="s">
+      <c r="K43" s="125" t="s">
         <v>300</v>
       </c>
-      <c r="L43" s="131"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="78"/>
-      <c r="O43" s="131"/>
-      <c r="P43" s="78"/>
+      <c r="L43" s="131">
+        <v>46240</v>
+      </c>
+      <c r="M43" s="78" t="s">
+        <v>302</v>
+      </c>
+      <c r="N43" s="78" t="s">
+        <v>303</v>
+      </c>
+      <c r="O43" s="131" t="s">
+        <v>302</v>
+      </c>
+      <c r="P43" s="78" t="s">
+        <v>303</v>
+      </c>
       <c r="Q43" s="78"/>
       <c r="R43" s="78"/>
       <c r="S43" s="78"/>
@@ -8569,7 +8581,7 @@
       <c r="V43" s="78"/>
       <c r="W43" s="78"/>
       <c r="X43" s="78"/>
-      <c r="Y43" s="192" t="s">
+      <c r="Y43" s="169" t="s">
         <v>301</v>
       </c>
     </row>
@@ -20364,11 +20376,6 @@
     <filterColumn colId="16" showButton="0"/>
   </autoFilter>
   <mergeCells count="17">
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="U3:U4"/>
     <mergeCell ref="L3:T3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -20381,6 +20388,11 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="U3:U4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
